--- a/HallFMBuggs.xlsx
+++ b/HallFMBuggs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D\Proj\DistrHall\SRSR.BPC\HallFieldMeter\toFix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spec260z\HallFieldMeterPro\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>R47 = 1k6, R45=4k7||100k = 4k25?</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>R11 - wrProtection - to GND (или джампер)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Сделать 3V3, которые идут на пробник для питания EEPROM защищенными от кз</t>
   </si>
 </sst>
 </file>
@@ -370,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
@@ -449,6 +452,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HallFMBuggs.xlsx
+++ b/HallFMBuggs.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>R47 = 1k6, R45=4k7||100k = 4k25?</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t xml:space="preserve"> Сделать 3V3, которые идут на пробник для питания EEPROM защищенными от кз</t>
+  </si>
+  <si>
+    <t>R71 make the same as R70, R59, R60</t>
   </si>
 </sst>
 </file>
@@ -373,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
@@ -460,6 +463,14 @@
         <v>9</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/HallFMBuggs.xlsx
+++ b/HallFMBuggs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spec260z\HallFieldMeterPro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spec260z\hwHallFMv1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>R47 = 1k6, R45=4k7||100k = 4k25?</t>
   </si>
@@ -57,14 +58,42 @@
   </si>
   <si>
     <t>R71 make the same as R70, R59, R60</t>
+  </si>
+  <si>
+    <t>to Order</t>
+  </si>
+  <si>
+    <t>RC0603FR-074K7L Yageo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chip 0603 4,7кОм, 1% Yageo  </t>
+  </si>
+  <si>
+    <t>R45</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>R47 = 1k5, R45=4k7-0805</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -93,9 +122,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -376,46 +409,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
-    <col min="2" max="2" width="81.44140625" customWidth="1"/>
+    <col min="2" max="2" width="66.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>46202</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46202</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46202</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46202</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46202</v>
       </c>
@@ -423,23 +460,23 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46202</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46202</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46203</v>
       </c>
@@ -447,15 +484,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46234</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46239</v>
       </c>
@@ -463,12 +500,54 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46252</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46287</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
